--- a/scripts/quality_check/source_diagnostics.xlsx
+++ b/scripts/quality_check/source_diagnostics.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2037</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="3">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2037</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2037</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="5">
